--- a/data/trans_orig/P33B_R1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R1-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>91794</t>
+          <t>100222</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74419</t>
+          <t>82927</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108572</t>
+          <t>119517</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>161385</t>
+          <t>177700</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145118</t>
+          <t>159751</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>178076</t>
+          <t>196728</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>253179</t>
+          <t>277922</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>229292</t>
+          <t>253031</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>278238</t>
+          <t>304764</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>542618</t>
+          <t>589406</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>525840</t>
+          <t>570111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>559993</t>
+          <t>606701</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>513482</t>
+          <t>554483</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>496791</t>
+          <t>535455</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>529749</t>
+          <t>572432</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1056100</t>
+          <t>1143889</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1031041</t>
+          <t>1117047</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1079987</t>
+          <t>1168780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,2%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674867</t>
+          <t>732183</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674867</t>
+          <t>732183</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674867</t>
+          <t>732183</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1309279</t>
+          <t>1421811</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1309279</t>
+          <t>1421811</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1309279</t>
+          <t>1421811</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>109568</t>
+          <t>118947</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51786</t>
+          <t>100209</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>146034</t>
+          <t>139922</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>197229</t>
+          <t>218447</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>176332</t>
+          <t>196664</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>218391</t>
+          <t>243200</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>306798</t>
+          <t>337394</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>207514</t>
+          <t>305194</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>356600</t>
+          <t>367244</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1083296</t>
+          <t>929970</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1046830</t>
+          <t>908995</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1141078</t>
+          <t>948708</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>760877</t>
+          <t>852391</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>739715</t>
+          <t>827638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>781774</t>
+          <t>874174</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1844173</t>
+          <t>1782361</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1794371</t>
+          <t>1752511</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1943457</t>
+          <t>1814561</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>76236</t>
+          <t>85060</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61438</t>
+          <t>68215</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98710</t>
+          <t>106216</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>115523</t>
+          <t>138787</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57538</t>
+          <t>121660</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154963</t>
+          <t>160757</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>191758</t>
+          <t>223846</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>129060</t>
+          <t>195183</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>232510</t>
+          <t>253214</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>628444</t>
+          <t>718013</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>605970</t>
+          <t>696857</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643242</t>
+          <t>734858</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>817843</t>
+          <t>673472</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>778403</t>
+          <t>651502</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>875828</t>
+          <t>690599</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1446288</t>
+          <t>1391486</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1405536</t>
+          <t>1362118</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1508986</t>
+          <t>1420149</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>87,92%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>138645</t>
+          <t>145119</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>118145</t>
+          <t>124961</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>161472</t>
+          <t>168934</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>231923</t>
+          <t>259059</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>185205</t>
+          <t>237460</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>261473</t>
+          <t>287583</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
+          <t>23,18%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>21,24%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>16,96%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>370568</t>
+          <t>404178</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>326131</t>
+          <t>371169</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>405466</t>
+          <t>437932</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>788186</t>
+          <t>844943</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>765359</t>
+          <t>821128</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>808686</t>
+          <t>865101</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,34 +1902,34 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>860104</t>
+          <t>858691</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>830554</t>
+          <t>830167</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>906822</t>
+          <t>880290</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>76,82%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>74,27%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>78,76%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>76,06%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>83,04%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2009</t>
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1648290</t>
+          <t>1703634</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1613392</t>
+          <t>1669880</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1692727</t>
+          <t>1736643</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1092027</t>
+          <t>1117750</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1092027</t>
+          <t>1117750</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1092027</t>
+          <t>1117750</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018858</t>
+          <t>2107812</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018858</t>
+          <t>2107812</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018858</t>
+          <t>2107812</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>416243</t>
+          <t>449347</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>331078</t>
+          <t>410856</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>468750</t>
+          <t>488805</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>706060</t>
+          <t>793993</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>561591</t>
+          <t>752721</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>771546</t>
+          <t>835932</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1122303</t>
+          <t>1243340</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>975390</t>
+          <t>1183311</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1214311</t>
+          <t>1308982</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3042544</t>
+          <t>3082333</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2990037</t>
+          <t>3042875</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3127709</t>
+          <t>3120824</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2952306</t>
+          <t>2939037</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2886820</t>
+          <t>2897098</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3096775</t>
+          <t>2980309</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5994851</t>
+          <t>6021370</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5902843</t>
+          <t>5955728</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6141764</t>
+          <t>6081399</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>83,71%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
